--- a/vlearn-app/public/quiz_excel/Day_04_System Prompt Engineering _ Tool Calling Engine/Day_04_Phan_01_20_Cau.xlsx
+++ b/vlearn-app/public/quiz_excel/Day_04_System Prompt Engineering _ Tool Calling Engine/Day_04_Phan_01_20_Cau.xlsx
@@ -801,7 +801,7 @@
       </c>
       <c r="G6" s="3" t="n"/>
       <c r="H6" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I6" s="4" t="n">
         <v>60</v>
@@ -809,7 +809,7 @@
       <c r="J6" s="3" t="n"/>
       <c r="K6" s="3" t="inlineStr">
         <is>
-          <t>Phân tích theo nguyên lý thiết kế: Xét hành động mà thành phần phía sau phải thực hiện với đầu ra.</t>
+          <t>Khi một dịch vụ downstream cần đọc 3 trường để quyết định nhánh xử lý, định dạng đầu ra phù hợp nhất là một JSON object có ba trường ổn định kèm schema và kiểu dữ liệu rõ ràng.</t>
         </is>
       </c>
     </row>
@@ -965,7 +965,7 @@
       </c>
       <c r="G9" s="3" t="n"/>
       <c r="H9" s="4" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I9" s="4" t="n">
         <v>60</v>
@@ -973,7 +973,7 @@
       <c r="J9" s="3" t="n"/>
       <c r="K9" s="3" t="inlineStr">
         <is>
-          <t>Phân tích theo nguyên lý thiết kế: So mức thay đổi kết quả của từng nấc, không nhìn tên kỹ thuật.</t>
+          <t>Baseline zero-shot đạt 18/20; thêm 1-shot nâng lên 19/20; thêm 2-shot vẫn 19/20 nhưng tăng 22% token. Quyết định tối ưu là giữ 1-shot và điều tra nguyên nhân lỗi cụ thể của ca còn lại, không thêm ví dụ thứ hai gây lãng phí chi phí.</t>
         </is>
       </c>
     </row>
@@ -1160,7 +1160,7 @@
       </c>
       <c r="C13" s="3" t="inlineStr">
         <is>
-          <t>o1 → o2 → o3 → o4</t>
+          <t>o4 → o3 → o2 → o1</t>
         </is>
       </c>
       <c r="D13" s="3" t="inlineStr">
@@ -1188,7 +1188,7 @@
       <c r="J13" s="3" t="n"/>
       <c r="K13" s="3" t="inlineStr">
         <is>
-          <t>Phân tích theo nguyên lý thiết kế: Nguồn dữ liệu không được chen vào chuỗi quyền chỉ vì chứa câu mệnh lệnh.</t>
+          <t>Hệ phân cấp thẩm quyền chỉ dẫn từ cao xuống thấp: Quy tắc hệ thống (System rules) (o4) -&gt; Chính sách developer (o3) -&gt; Người dùng (User instructions) (o2) -&gt; Trang web/dữ liệu không tin cậy được truy xuất (o1).</t>
         </is>
       </c>
     </row>
@@ -1347,7 +1347,7 @@
       </c>
       <c r="G16" s="3" t="n"/>
       <c r="H16" s="4" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I16" s="4" t="n">
         <v>60</v>
@@ -1355,7 +1355,7 @@
       <c r="J16" s="3" t="n"/>
       <c r="K16" s="3" t="inlineStr">
         <is>
-          <t>Phân tích theo nguyên lý thiết kế: Phân biệt content default với permission tạo side effect.</t>
+          <t>Người dùng yêu cầu viết email lịch sự nhưng chưa nêu câu chào. Vì câu chào không tạo tác động phụ nguy hiểm và email chưa gửi thật, hành vi đúng là soạn bản nháp với lựa chọn mặc định lịch sự được nêu rõ, chưa gửi.</t>
         </is>
       </c>
     </row>
@@ -1468,7 +1468,7 @@
       </c>
       <c r="H18" s="4" t="inlineStr">
         <is>
-          <t>1,2</t>
+          <t>1,2,5</t>
         </is>
       </c>
       <c r="I18" s="4" t="n">
@@ -1477,7 +1477,7 @@
       <c r="J18" s="3" t="n"/>
       <c r="K18" s="3" t="inlineStr">
         <is>
-          <t>Phân tích theo nguyên lý thiết kế: Với mỗi item, hỏi nếu xóa nó thì verdict hoặc boundary có thể đổi không.</t>
+          <t>Thông tin cần giữ trong packet quyết định hoàn tiền booking B17: Chính sách hủy 48h đúng phiên bản (a), Thời gian check-in còn 36h (b), và Điều khoản non-refundable riêng của booking B17 nếu có (e). Sở thích phòng (c) và lịch sử chuyến đi cũ (d) không ảnh hưởng đến điều kiện hoàn tiền.</t>
         </is>
       </c>
     </row>
@@ -1636,7 +1636,7 @@
       </c>
       <c r="G21" s="3" t="n"/>
       <c r="H21" s="4" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I21" s="4" t="n">
         <v>60</v>
@@ -1644,7 +1644,7 @@
       <c r="J21" s="3" t="n"/>
       <c r="K21" s="3" t="inlineStr">
         <is>
-          <t>Phân tích theo nguyên lý thiết kế: Hãy xét tác động mạnh nhất có thể xảy ra khi gọi tool hợp lệ.</t>
+          <t>Tool `get_or_create_profile(email)` có nhánh tạo mới làm thay đổi trạng thái trong cơ sở dữ liệu nếu hồ sơ chưa tồn tại, do đó phải được phân loại vào nhóm hành động/ghi dữ liệu (write action).</t>
         </is>
       </c>
     </row>
